--- a/output/generated-database-cloud9.xlsx
+++ b/output/generated-database-cloud9.xlsx
@@ -453,646 +453,385 @@
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"26/05/1970"</t>
+"DOB: 16/11/1950"</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"AIDEN O'CONNOR"</t>
+"Graham Green"</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Hospital Number: 9990001(d)"</t>
+"Hospital Number: 9999005"</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"NHS Number: 9990000001(c)"</t>
+"NHS Number: 9998009005"</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Male(e)"</t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: MEDIUM]
-Source evidence:
-"Colonoscopy :"</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy :"</t>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"At 13cm from insertion there was a malignant looking mass with an abnormal pit pattern suspicious features for malignancy."</t>
+"Male"</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Relevant history includes chronic kidney disease stage 3."</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Diagnosis: ADENOCARCINOMA, NOT OTHERWISE SPECIFIED
-Histo: Adenocarcinoma."</t>
+"Diagnosis: Sigmoid adenocarcinoma"</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
-        <t>[Confidence: MEDIUM]
-Source evidence:
-"Colonoscopy noted - Histo: Adenocarcinoma."</t>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MMR deficient"</t>
+        <t>[Confidence: LOW]
+Source evidence:
+"Diagnosis: Sigmoid adenocarcinoma"</t>
       </text>
     </comment>
     <comment ref="T2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"CT 29/02/2025"</t>
+"CT TAP on 06/09/2024"</t>
+      </text>
+    </comment>
+    <comment ref="V2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"no enlarged mesenteric nodes"</t>
+      </text>
+    </comment>
+    <comment ref="X2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"no distant metastases"</t>
       </text>
     </comment>
     <comment ref="Y2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Indeterminate retroperitoneal lymph nodes."</t>
+"sigmoid colon thickening"</t>
       </text>
     </comment>
     <comment ref="Z2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Indeterminate retroperitoneal lymph nodes."</t>
+"sigmoid colon thickening"</t>
       </text>
     </comment>
     <comment ref="AA2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Colorectal Multidisciplinary Meeting 07/03/2025"</t>
+"13/09/2024(i)"</t>
+      </text>
+    </comment>
+    <comment ref="AB2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Refer for colorectal surgical review."</t>
       </text>
     </comment>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"30/03/1944 Age: 81 Years(a)"</t>
+"DOB: 18/08/1937"</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"ZIAD AL-FARSI(b)"</t>
+"Ava Clarke"</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Hospital Number: 9990002(d)"</t>
+"Hospital Number: 9999006"</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"NHS Number: 9990000002(c)"</t>
+"NHS Number: 9998009006"</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Male(e)"</t>
+"Female"</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Known prior lymphoma, treated"</t>
+"Relevant history includes history of breast cancer (treated)."</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Known prior lymphoma, treated"</t>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
+"history of breast cancer"</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
+"Diagnosis: Villous adenoma with focal invasion"</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"MRI 4/3/25"</t>
+"MRI pelvis on 31/10/2024"</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear"</t>
+"T1 sm2/3"</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear"</t>
+"N0"</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear"</t>
+"EMVI negative"</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear"</t>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear"</t>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT 22/2/2025: no lymphadenopathy. New semi-annular thickening in rectum"</t>
-      </text>
-    </comment>
-    <comment ref="V3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT 22/2/2025: no lymphadenopathy. New semi-annular thickening in rectum"</t>
+"CRM clear"</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Colorectal Multidisciplinary Meeting 07/03/2025(i)"</t>
+"Colorectal Multidisciplinary Meeting 14/11/2024(i)"</t>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Refer for colorectal surgical review."</t>
       </text>
     </comment>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"19/12/1974"</t>
+"DOB: 27/12/1947"</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"AISHA MOHAMMED"</t>
+"Mason Barker"</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"9990003"</t>
+"Hospital Number: 9999007"</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"9990000003"</t>
+"NHS Number: 9998009007"</t>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
+"Male"</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Relevant history includes ischaemic heart disease."</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Tubular adenoma with HGD"</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CT TAP on 14/06/2024"</t>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"multiple enlarged mesenteric nodes"</t>
+      </text>
+    </comment>
+    <comment ref="X4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"no distant metastases."</t>
+      </text>
+    </comment>
+    <comment ref="Y4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"upper rectum thickening with multiple enlarged mesenteric nodes; no distant metastases."</t>
+      </text>
+    </comment>
+    <comment ref="AA4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colorectal Multidisciplinary Meeting — 21/06/2024(i)"</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 08/08/1951"</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Freida Smale"</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999008"</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009008"</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
 "Female"</t>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: MEDIUM]
-Source evidence:
-"Multiple polyps within the colon, largest is 3 cm in the descending colon – 2 cm polyp located at the ICV and multiple diminutive polyps seen elsewhere. Biopsies taken."</t>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Repeat colonoscopy"</t>
-      </text>
-    </comment>
-    <comment ref="J4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Multiple polyps within the colon, largest is 3 cm in the descending colon – 2 cm polyp located at the ICV and multiple diminutive polyps seen elsewhere."</t>
-      </text>
-    </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Descending colon polyp – well differentiated adenocarcinoma 
-Other polyps – tubular adenoma with low grade dysplasia"</t>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: MEDIUM]
-Source evidence:
-"Biopsies taken."</t>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: MEDIUM]
-Source evidence:
-"CT TAP:"</t>
-      </text>
-    </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"No lymphadenopathy."</t>
-      </text>
-    </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"No metastases."</t>
-      </text>
-    </comment>
-    <comment ref="AA4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"07/03/2025"</t>
-      </text>
-    </comment>
-    <comment ref="AB4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"To see consultant next week to discuss possible surgery"</t>
-      </text>
-    </comment>
-    <comment ref="A5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"25/02/1943"</t>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MATTEO ROSSI"</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"9990004"</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"9990000004"</t>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Male"</t>
-      </text>
-    </comment>
     <comment ref="K5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"ADENOCARCINOMA, NOT OTHERWISE SPECIFIED"</t>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Feb 2025 – adenocarcinoma"</t>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"deficient MMR"</t>
+"Diagnosis: Right‑sided colonic tumour"</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI pelvis on 30/07/2024"</t>
       </text>
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"T2"</t>
+"T3a"</t>
       </text>
     </comment>
     <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"N0"</t>
+"N1c"</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"EMVI negative"</t>
+"EMVI positive."</t>
       </text>
     </comment>
     <comment ref="R5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"CRM clear"</t>
-      </text>
-    </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"PSW clear"</t>
+"CRM clear,"</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"07/03/2025"</t>
+"Colorectal Multidisciplinary Meeting 20/08/2024(i)"</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"RE entering watch and wait"</t>
-      </text>
-    </comment>
-    <comment ref="AM5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CRT to downstage"</t>
-      </text>
-    </comment>
-    <comment ref="AU5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 1/3/25"</t>
-      </text>
-    </comment>
-    <comment ref="AV5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"may represent complete response"</t>
-      </text>
-    </comment>
-    <comment ref="AW5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"staging unchanged"</t>
-      </text>
-    </comment>
-    <comment ref="AX5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"staging unchanged"</t>
-      </text>
-    </comment>
-    <comment ref="AY5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"staging unchanged"</t>
-      </text>
-    </comment>
-    <comment ref="AZ5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"staging unchanged"</t>
-      </text>
-    </comment>
-    <comment ref="BA5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"staging unchanged"</t>
-      </text>
-    </comment>
-    <comment ref="BM5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"scar seen"</t>
-      </text>
-    </comment>
-    <comment ref="BP5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colorectal Multidisciplinary Meeting 07/03/2025(i)"</t>
-      </text>
-    </comment>
-    <comment ref="BV5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colorectal Multidisciplinary Meeting 07/03/2025(i)"</t>
-      </text>
-    </comment>
-    <comment ref="A6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"DOB: 16/11/1950"</t>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Graham Green"</t>
-      </text>
-    </comment>
-    <comment ref="C6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Hospital Number: 9999005"</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"NHS Number: 9998009005"</t>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Male"</t>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Relevant history includes chronic kidney disease stage 3."</t>
-      </text>
-    </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Diagnosis: Sigmoid adenocarcinoma"</t>
-      </text>
-    </comment>
-    <comment ref="L6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: LOW]
-Source evidence:
-"Diagnosis: Sigmoid adenocarcinoma"</t>
-      </text>
-    </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT TAP on 06/09/2024"</t>
-      </text>
-    </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"no enlarged mesenteric nodes"</t>
-      </text>
-    </comment>
-    <comment ref="X6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"no distant metastases"</t>
-      </text>
-    </comment>
-    <comment ref="Y6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"sigmoid colon thickening"</t>
-      </text>
-    </comment>
-    <comment ref="Z6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"sigmoid colon thickening"</t>
-      </text>
-    </comment>
-    <comment ref="AA6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colorectal Multidisciplinary Meeting 13/09/2024(i)"</t>
-      </text>
-    </comment>
-    <comment ref="AB6" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Refer for colorectal surgical review."</t>
+"Plan neoadjuvant CRT"</t>
       </text>
     </comment>
   </commentList>
@@ -1420,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS6"/>
+  <dimension ref="A1:CS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.28515625" customWidth="1" min="1" max="1"/>
@@ -1913,59 +1652,61 @@
     </row>
     <row r="2" ht="75" customFormat="1" customHeight="1" s="28">
       <c r="A2" s="29" t="n">
-        <v>25714</v>
+        <v>18583</v>
       </c>
       <c r="B2" s="28" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>GG</t>
         </is>
       </c>
       <c r="C2" s="28" t="n">
-        <v>9990001</v>
+        <v>9999005</v>
       </c>
       <c r="D2" s="28" t="n">
-        <v>9990000001</v>
+        <v>9998009005</v>
       </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="28" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Sigmoid adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="I2" s="28" t="inlineStr">
-        <is>
-          <t>Colonoscopy complete</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>At 13cm from insertion there was a malignant looking mass with an abnormal pit pattern suspicious features for malignancy.</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Adenocarcinoma</t>
-        </is>
-      </c>
-      <c r="L2" s="28" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="M2" s="28" t="inlineStr">
-        <is>
-          <t>Deficient</t>
-        </is>
-      </c>
+      <c r="M2" s="28" t="n"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>29/02/2025</t>
+          <t>06/09/2024</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1975,12 +1716,17 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Indeterminate retroperitoneal lymph nodes.</t>
+          <t>sigmoid colon thickening</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>13/09/2024</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Refer for colorectal surgical review</t>
         </is>
       </c>
       <c r="BV2" s="1" t="n"/>
@@ -2001,22 +1747,22 @@
     </row>
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="29" t="n">
-        <v>16161</v>
+        <v>13745</v>
       </c>
       <c r="B3" s="28" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C3" s="28" t="n">
-        <v>9990002</v>
+        <v>9999006</v>
       </c>
       <c r="D3" s="28" t="n">
-        <v>9990000002</v>
+        <v>9998009006</v>
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
@@ -2026,27 +1772,15 @@
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>lymphoma</t>
-        </is>
-      </c>
-      <c r="H3" s="28" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="I3" s="28" t="inlineStr">
-        <is>
-          <t>Colonoscopy complete</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>polypoidal lesion in the low rectum</t>
-        </is>
-      </c>
+          <t>breast</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="28" t="n"/>
+      <c r="J3" s="1" t="n"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>adenocarcinoma, poorly differentiated</t>
+          <t>Villous adenoma with focal invasion</t>
         </is>
       </c>
       <c r="L3" s="28" t="inlineStr">
@@ -2057,47 +1791,37 @@
       <c r="M3" s="28" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>04/03/2025</t>
+          <t>31/10/2024</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3c</t>
+          <t>1 sm2/3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1c</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>threatened</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
           <t>clear</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>22/02/2025</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>14/11/2024</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Refer for colorectal surgical review</t>
         </is>
       </c>
       <c r="BV3" s="1" t="n"/>
@@ -2118,75 +1842,67 @@
     </row>
     <row r="4" ht="75" customHeight="1">
       <c r="A4" s="29" t="n">
-        <v>27382</v>
+        <v>17528</v>
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="C4" s="28" t="n">
-        <v>9990003</v>
+        <v>9999007</v>
       </c>
       <c r="D4" s="28" t="n">
-        <v>9990000003</v>
+        <v>9998009007</v>
       </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="F4" s="28" t="n"/>
-      <c r="G4" s="28" t="n"/>
-      <c r="H4" s="28" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="I4" s="28" t="inlineStr">
-        <is>
-          <t>Colonoscopy complete</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>Multiple polyps within the colon, largest is 3 cm in the descending colon – 2 cm polyp located at the ICV and multiple diminutive polyps seen elsewhere.</t>
-        </is>
-      </c>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>well differentiated adenocarcinoma; tubular adenoma with low grade dysplasia</t>
-        </is>
-      </c>
-      <c r="L4" s="28" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
+          <t>Tubular adenoma with HGD</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="n"/>
       <c r="M4" s="28" t="n"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>14/06/2024</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Discuss possible surgery</t>
+          <t>21/06/2024</t>
         </is>
       </c>
       <c r="BV4" s="1" t="n"/>
@@ -2207,65 +1923,54 @@
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="29" t="n">
-        <v>15762</v>
+        <v>18848</v>
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>MR</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>9990004</v>
+        <v>9999008</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>9990000004</v>
+        <v>9998009008</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
       <c r="H5" s="28" t="n"/>
       <c r="I5" s="28" t="n"/>
       <c r="J5" s="1" t="n"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>ADENOCARCINOMA, NOT OTHERWISE SPECIFIED</t>
-        </is>
-      </c>
-      <c r="L5" s="28" t="inlineStr">
-        <is>
-          <t>Feb 2025</t>
-        </is>
-      </c>
-      <c r="M5" s="28" t="inlineStr">
-        <is>
-          <t>Deficient</t>
+          <t>Right‑sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>30/07/2024</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3a</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1c</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2273,76 +1978,17 @@
           <t>clear</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>watch and wait</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>01/03/2025</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>may represent complete response</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>scar seen</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>07/03/2025</t>
-        </is>
-      </c>
-      <c r="BV5" s="1" t="inlineStr">
-        <is>
-          <t>07/03/2025</t>
-        </is>
-      </c>
+          <t>neoadjuvant CRT</t>
+        </is>
+      </c>
+      <c r="BV5" s="1" t="n"/>
       <c r="BW5" s="1" t="n"/>
       <c r="BX5" s="1" t="n"/>
       <c r="BY5" s="1" t="n"/>
@@ -2358,101 +2004,6 @@
       <c r="CI5" s="1" t="n"/>
       <c r="CJ5" s="1" t="n"/>
     </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="29" t="n">
-        <v>18583</v>
-      </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>9999005</v>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>9998009005</v>
-      </c>
-      <c r="E6" s="28" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>Sigmoid adenocarcinoma</t>
-        </is>
-      </c>
-      <c r="L6" s="28" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="M6" s="28" t="n"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>06/09/2024</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>sigmoid colon thickening</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>13/09/2024</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Refer for colorectal surgical review</t>
-        </is>
-      </c>
-      <c r="BV6" s="1" t="n"/>
-      <c r="BW6" s="1" t="n"/>
-      <c r="BX6" s="1" t="n"/>
-      <c r="BY6" s="1" t="n"/>
-      <c r="BZ6" s="1" t="n"/>
-      <c r="CA6" s="1" t="n"/>
-      <c r="CB6" s="1" t="n"/>
-      <c r="CC6" s="1" t="n"/>
-      <c r="CD6" s="1" t="n"/>
-      <c r="CE6" s="1" t="n"/>
-      <c r="CF6" s="1" t="n"/>
-      <c r="CG6" s="1" t="n"/>
-      <c r="CH6" s="1" t="n"/>
-      <c r="CI6" s="1" t="n"/>
-      <c r="CJ6" s="1" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2465,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ6"/>
+  <dimension ref="A1:CJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,472 +2476,283 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[high] 26/05/1970</t>
+          <t>[high] DOB: 16/11/1950</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[high] AIDEN O'CONNOR</t>
+          <t>[high] Graham Green</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[high] Hospital Number: 9990001(d)</t>
+          <t>[high] Hospital Number: 9999005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[high] NHS Number: 9990000001(c)</t>
+          <t>[high] NHS Number: 9998009005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[high] Male(e)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[medium] Colonoscopy :</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy :</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[high] At 13cm from insertion there was a malignant looking mass with an abnormal pit pattern suspicious features for malignancy.</t>
+          <t>[high] Male</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[high] Relevant history includes chronic kidney disease stage 3.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[high] Diagnosis: ADENOCARCINOMA, NOT OTHERWISE SPECIFIED
-Histo: Adenocarcinoma.</t>
+          <t>[high] Diagnosis: Sigmoid adenocarcinoma</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[medium] Colonoscopy noted - Histo: Adenocarcinoma.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>[high] MMR deficient</t>
+          <t>[low] Diagnosis: Sigmoid adenocarcinoma</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[high] CT 29/02/2025</t>
+          <t>[high] CT TAP on 06/09/2024</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>[high] no enlarged mesenteric nodes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[high] no distant metastases</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[high] Indeterminate retroperitoneal lymph nodes.</t>
+          <t>[high] sigmoid colon thickening</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[high] Indeterminate retroperitoneal lymph nodes.</t>
+          <t>[high] sigmoid colon thickening</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 07/03/2025</t>
+          <t>[high] 13/09/2024(i)</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>[high] Refer for colorectal surgical review.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[high] 30/03/1944 Age: 81 Years(a)</t>
+          <t>[high] DOB: 18/08/1937</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[high] ZIAD AL-FARSI(b)</t>
+          <t>[high] Ava Clarke</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[high] Hospital Number: 9990002(d)</t>
+          <t>[high] Hospital Number: 9999006</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[high] NHS Number: 9990000002(c)</t>
+          <t>[high] NHS Number: 9998009006</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[high] Male(e)</t>
+          <t>[high] Female</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[high] Known prior lymphoma, treated</t>
+          <t>[high] Relevant history includes history of breast cancer (treated).</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[high] Known prior lymphoma, treated</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[high] polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+          <t>[high] history of breast cancer</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[high] biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+          <t>[high] Diagnosis: Villous adenoma with focal invasion</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[high] MRI 4/3/25</t>
+          <t>[high] MRI pelvis on 31/10/2024</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[high] T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear</t>
+          <t>[high] T1 sm2/3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[high] T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear</t>
+          <t>[high] N0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[high] T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear</t>
+          <t>[high] EMVI negative</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[high] T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[high] T3c, N1c, CRM/ISP unsafe, EMVI positive, PSW clear</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[high] CT 22/2/2025: no lymphadenopathy. New semi-annular thickening in rectum</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>[high] CT 22/2/2025: no lymphadenopathy. New semi-annular thickening in rectum</t>
+          <t>[high] CRM clear</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 07/03/2025(i)</t>
+          <t>[high] Colorectal Multidisciplinary Meeting 14/11/2024(i)</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[high] Refer for colorectal surgical review.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[high] 19/12/1974</t>
+          <t>[high] DOB: 27/12/1947</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[high] AISHA MOHAMMED</t>
+          <t>[high] Mason Barker</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[high] 9990003</t>
+          <t>[high] Hospital Number: 9999007</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[high] 9990000003</t>
+          <t>[high] NHS Number: 9998009007</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[high] Female</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[medium] Multiple polyps within the colon, largest is 3 cm in the descending colon – 2 cm polyp located at the ICV and multiple diminutive polyps seen elsewhere. Biopsies taken.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>[high] Repeat colonoscopy</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[high] Multiple polyps within the colon, largest is 3 cm in the descending colon – 2 cm polyp located at the ICV and multiple diminutive polyps seen elsewhere.</t>
+          <t>[high] Male</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[high] Relevant history includes ischaemic heart disease.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[high] Descending colon polyp – well differentiated adenocarcinoma 
-Other polyps – tubular adenoma with low grade dysplasia</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>[medium] Biopsies taken.</t>
+          <t>[high] Diagnosis: Tubular adenoma with HGD</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>[medium] CT TAP:</t>
+          <t>[high] CT TAP on 14/06/2024</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>[high] No lymphadenopathy.</t>
+          <t>[high] multiple enlarged mesenteric nodes</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[high] No metastases.</t>
+          <t>[high] no distant metastases.</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[high] upper rectum thickening with multiple enlarged mesenteric nodes; no distant metastases.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[high] 07/03/2025</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>[high] To see consultant next week to discuss possible surgery</t>
+          <t>[high] Colorectal Multidisciplinary Meeting — 21/06/2024(i)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[high] 25/02/1943</t>
+          <t>[high] DOB: 08/08/1951</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[high] MATTEO ROSSI</t>
+          <t>[high] Freida Smale</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[high] 9990004</t>
+          <t>[high] Hospital Number: 9999008</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[high] 9990000004</t>
+          <t>[high] NHS Number: 9998009008</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[high] Male</t>
+          <t>[high] Female</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[high] ADENOCARCINOMA, NOT OTHERWISE SPECIFIED</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>[high] Feb 2025 – adenocarcinoma</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>[high] deficient MMR</t>
+          <t>[high] Diagnosis: Right‑sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[high] MRI pelvis on 30/07/2024</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[high] T2</t>
+          <t>[high] T3a</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[high] N0</t>
+          <t>[high] N1c</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[high] EMVI negative</t>
+          <t>[high] EMVI positive.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[high] CRM clear</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>[high] PSW clear</t>
+          <t>[high] CRM clear,</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[high] 07/03/2025</t>
+          <t>[high] Colorectal Multidisciplinary Meeting 20/08/2024(i)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[high] RE entering watch and wait</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>[high] CRT to downstage</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>[high] MRI 1/3/25</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>[high] may represent complete response</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>[high] staging unchanged</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>[high] staging unchanged</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>[high] staging unchanged</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>[high] staging unchanged</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>[high] staging unchanged</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>[high] scar seen</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 07/03/2025(i)</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 07/03/2025(i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[high] DOB: 16/11/1950</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[high] Graham Green</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[high] Hospital Number: 9999005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[high] NHS Number: 9998009005</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[high] Male</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[high] Relevant history includes chronic kidney disease stage 3.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[high] Diagnosis: Sigmoid adenocarcinoma</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>[low] Diagnosis: Sigmoid adenocarcinoma</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>[high] CT TAP on 06/09/2024</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>[high] no enlarged mesenteric nodes</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[high] no distant metastases</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>[high] sigmoid colon thickening</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>[high] sigmoid colon thickening</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 13/09/2024(i)</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>[high] Refer for colorectal surgical review.</t>
+          <t>[high] Plan neoadjuvant CRT</t>
         </is>
       </c>
     </row>

--- a/output/generated-database-cloud9.xlsx
+++ b/output/generated-database-cloud9.xlsx
@@ -453,28 +453,28 @@
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"DOB: 16/11/1950"</t>
+"30/03/1944 Age"</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Graham Green"</t>
+"ZIAD AL-FARSI(b)"</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Hospital Number: 9999005"</t>
+"Hospital Number: 9990002"</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"NHS Number: 9998009005"</t>
+"NHS Number: 9990000002"</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
@@ -488,350 +488,168 @@
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Relevant history includes chronic kidney disease stage 3."</t>
+"lymphoma"</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"lymphoma"</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Diagnosis: Sigmoid adenocarcinoma"</t>
+"Diagnosis: ADENOCARCINOMA, NOT OTHERWISE SPECIFIED"</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
-        <t>[Confidence: LOW]
-Source evidence:
-"Diagnosis: Sigmoid adenocarcinoma"</t>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25"</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"T3c"</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"N1c"</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"EMVI positive"</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CRM/ISP unsafe"</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"PSW clear"</t>
       </text>
     </comment>
     <comment ref="T2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"CT TAP on 06/09/2024"</t>
+"CT 22/2/2025"</t>
       </text>
     </comment>
     <comment ref="V2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"no enlarged mesenteric nodes"</t>
+"CT 22/2/2025: no lymphadenopathy."</t>
       </text>
     </comment>
     <comment ref="X2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"no distant metastases"</t>
-      </text>
-    </comment>
-    <comment ref="Y2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"sigmoid colon thickening"</t>
-      </text>
-    </comment>
-    <comment ref="Z2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"sigmoid colon thickening"</t>
+"CT 22/2/2025: no lymphadenopathy."</t>
       </text>
     </comment>
     <comment ref="AA2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"13/09/2024(i)"</t>
+"07/03/2025"</t>
       </text>
     </comment>
     <comment ref="AB2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Refer for colorectal surgical review."</t>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"DOB: 18/08/1937"</t>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Ava Clarke"</t>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Hospital Number: 9999006"</t>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"NHS Number: 9998009006"</t>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Female"</t>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Relevant history includes history of breast cancer (treated)."</t>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"history of breast cancer"</t>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Diagnosis: Villous adenoma with focal invasion"</t>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI pelvis on 31/10/2024"</t>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"T1 sm2/3"</t>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"N0"</t>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"EMVI negative"</t>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CRM clear"</t>
-      </text>
-    </comment>
-    <comment ref="AA3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colorectal Multidisciplinary Meeting 14/11/2024(i)"</t>
-      </text>
-    </comment>
-    <comment ref="AB3" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Refer for colorectal surgical review."</t>
-      </text>
-    </comment>
-    <comment ref="A4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"DOB: 27/12/1947"</t>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Mason Barker"</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Hospital Number: 9999007"</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"NHS Number: 9998009007"</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Male"</t>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Relevant history includes ischaemic heart disease."</t>
-      </text>
-    </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Diagnosis: Tubular adenoma with HGD"</t>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT TAP on 14/06/2024"</t>
-      </text>
-    </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"multiple enlarged mesenteric nodes"</t>
-      </text>
-    </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"no distant metastases."</t>
-      </text>
-    </comment>
-    <comment ref="Y4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"upper rectum thickening with multiple enlarged mesenteric nodes; no distant metastases."</t>
-      </text>
-    </comment>
-    <comment ref="AA4" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colorectal Multidisciplinary Meeting — 21/06/2024(i)"</t>
-      </text>
-    </comment>
-    <comment ref="A5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"DOB: 08/08/1951"</t>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Freida Smale"</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Hospital Number: 9999008"</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"NHS Number: 9998009008"</t>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Female"</t>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Diagnosis: Right‑sided colonic tumour"</t>
-      </text>
-    </comment>
-    <comment ref="N5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI pelvis on 30/07/2024"</t>
-      </text>
-    </comment>
-    <comment ref="O5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"T3a"</t>
-      </text>
-    </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"N1c"</t>
-      </text>
-    </comment>
-    <comment ref="Q5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"EMVI positive."</t>
-      </text>
-    </comment>
-    <comment ref="R5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CRM clear,"</t>
-      </text>
-    </comment>
-    <comment ref="AA5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colorectal Multidisciplinary Meeting 20/08/2024(i)"</t>
-      </text>
-    </comment>
-    <comment ref="AB5" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Plan neoadjuvant CRT"</t>
+"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
+      </text>
+    </comment>
+    <comment ref="AU2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted."</t>
+      </text>
+    </comment>
+    <comment ref="AW2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
+      </text>
+    </comment>
+    <comment ref="AX2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
+      </text>
+    </comment>
+    <comment ref="AY2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
+      </text>
+    </comment>
+    <comment ref="AZ2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
+      </text>
+    </comment>
+    <comment ref="BA2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
       </text>
     </comment>
   </commentList>
@@ -1159,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS5"/>
+  <dimension ref="A1:CS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.28515625" customWidth="1" min="1" max="1"/>
@@ -1652,18 +1470,18 @@
     </row>
     <row r="2" ht="75" customFormat="1" customHeight="1" s="28">
       <c r="A2" s="29" t="n">
-        <v>18583</v>
+        <v>16161</v>
       </c>
       <c r="B2" s="28" t="inlineStr">
         <is>
-          <t>GG</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="C2" s="28" t="n">
-        <v>9999005</v>
+        <v>9990002</v>
       </c>
       <c r="D2" s="28" t="n">
-        <v>9998009005</v>
+        <v>9990000002</v>
       </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
@@ -1672,31 +1490,73 @@
       </c>
       <c r="F2" s="28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G2" s="28" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H2" s="28" t="n"/>
-      <c r="I2" s="28" t="n"/>
-      <c r="J2" s="1" t="n"/>
+          <t>lymphoma</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Colonoscopy complete</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Sigmoid adenocarcinoma</t>
+          <t>ADENOCARCINOMA, NOT OTHERWISE SPECIFIED</t>
         </is>
       </c>
       <c r="L2" s="28" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="M2" s="28" t="n"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>04/03/2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3c</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>threatened</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>06/09/2024</t>
+          <t>22/02/2025</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1709,24 +1569,44 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>sigmoid colon thickening</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>13/09/2024</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Refer for colorectal surgical review</t>
+          <t>straight to surgery</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>4/3/25</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>3c</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>threatened</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>clear</t>
         </is>
       </c>
       <c r="BV2" s="1" t="n"/>
@@ -1745,265 +1625,6 @@
       <c r="CI2" s="1" t="n"/>
       <c r="CJ2" s="1" t="n"/>
     </row>
-    <row r="3" ht="75" customHeight="1">
-      <c r="A3" s="29" t="n">
-        <v>13745</v>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="n">
-        <v>9999006</v>
-      </c>
-      <c r="D3" s="28" t="n">
-        <v>9998009006</v>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>breast</t>
-        </is>
-      </c>
-      <c r="H3" s="28" t="n"/>
-      <c r="I3" s="28" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Villous adenoma with focal invasion</t>
-        </is>
-      </c>
-      <c r="L3" s="28" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="M3" s="28" t="n"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>31/10/2024</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1 sm2/3</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>14/11/2024</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Refer for colorectal surgical review</t>
-        </is>
-      </c>
-      <c r="BV3" s="1" t="n"/>
-      <c r="BW3" s="1" t="n"/>
-      <c r="BX3" s="1" t="n"/>
-      <c r="BY3" s="1" t="n"/>
-      <c r="BZ3" s="1" t="n"/>
-      <c r="CA3" s="1" t="n"/>
-      <c r="CB3" s="1" t="n"/>
-      <c r="CC3" s="1" t="n"/>
-      <c r="CD3" s="1" t="n"/>
-      <c r="CE3" s="1" t="n"/>
-      <c r="CF3" s="1" t="n"/>
-      <c r="CG3" s="1" t="n"/>
-      <c r="CH3" s="1" t="n"/>
-      <c r="CI3" s="1" t="n"/>
-      <c r="CJ3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="29" t="n">
-        <v>17528</v>
-      </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="C4" s="28" t="n">
-        <v>9999007</v>
-      </c>
-      <c r="D4" s="28" t="n">
-        <v>9998009007</v>
-      </c>
-      <c r="E4" s="28" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="28" t="n"/>
-      <c r="I4" s="28" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>Tubular adenoma with HGD</t>
-        </is>
-      </c>
-      <c r="L4" s="28" t="n"/>
-      <c r="M4" s="28" t="n"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>14/06/2024</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>21/06/2024</t>
-        </is>
-      </c>
-      <c r="BV4" s="1" t="n"/>
-      <c r="BW4" s="1" t="n"/>
-      <c r="BX4" s="1" t="n"/>
-      <c r="BY4" s="1" t="n"/>
-      <c r="BZ4" s="1" t="n"/>
-      <c r="CA4" s="1" t="n"/>
-      <c r="CB4" s="1" t="n"/>
-      <c r="CC4" s="1" t="n"/>
-      <c r="CD4" s="1" t="n"/>
-      <c r="CE4" s="1" t="n"/>
-      <c r="CF4" s="1" t="n"/>
-      <c r="CG4" s="1" t="n"/>
-      <c r="CH4" s="1" t="n"/>
-      <c r="CI4" s="1" t="n"/>
-      <c r="CJ4" s="1" t="n"/>
-    </row>
-    <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="29" t="n">
-        <v>18848</v>
-      </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="n">
-        <v>9999008</v>
-      </c>
-      <c r="D5" s="28" t="n">
-        <v>9998009008</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>Right‑sided colonic tumour</t>
-        </is>
-      </c>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>30/07/2024</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>3a</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>1c</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>20/08/2024</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>neoadjuvant CRT</t>
-        </is>
-      </c>
-      <c r="BV5" s="1" t="n"/>
-      <c r="BW5" s="1" t="n"/>
-      <c r="BX5" s="1" t="n"/>
-      <c r="BY5" s="1" t="n"/>
-      <c r="BZ5" s="1" t="n"/>
-      <c r="CA5" s="1" t="n"/>
-      <c r="CB5" s="1" t="n"/>
-      <c r="CC5" s="1" t="n"/>
-      <c r="CD5" s="1" t="n"/>
-      <c r="CE5" s="1" t="n"/>
-      <c r="CF5" s="1" t="n"/>
-      <c r="CG5" s="1" t="n"/>
-      <c r="CH5" s="1" t="n"/>
-      <c r="CI5" s="1" t="n"/>
-      <c r="CJ5" s="1" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2016,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ5"/>
+  <dimension ref="A1:CJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2476,22 +2097,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[high] DOB: 16/11/1950</t>
+          <t>[high] 30/03/1944 Age</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[high] Graham Green</t>
+          <t>[high] ZIAD AL-FARSI(b)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[high] Hospital Number: 9999005</t>
+          <t>[high] Hospital Number: 9990002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[high] NHS Number: 9998009005</t>
+          <t>[high] NHS Number: 9990000002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2501,258 +2122,122 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[high] Relevant history includes chronic kidney disease stage 3.</t>
+          <t>[high] lymphoma</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[high] lymphoma</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[high] Diagnosis: Sigmoid adenocarcinoma</t>
+          <t>[high] Diagnosis: ADENOCARCINOMA, NOT OTHERWISE SPECIFIED</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[low] Diagnosis: Sigmoid adenocarcinoma</t>
+          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>[high] T3c</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[high] N1c</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>[high] EMVI positive</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>[high] CRM/ISP unsafe</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>[high] PSW clear</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[high] CT TAP on 06/09/2024</t>
+          <t>[high] CT 22/2/2025</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>[high] no enlarged mesenteric nodes</t>
+          <t>[high] CT 22/2/2025: no lymphadenopathy.</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[high] no distant metastases</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>[high] sigmoid colon thickening</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>[high] sigmoid colon thickening</t>
+          <t>[high] CT 22/2/2025: no lymphadenopathy.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[high] 13/09/2024(i)</t>
+          <t>[high] 07/03/2025</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[high] Refer for colorectal surgical review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[high] DOB: 18/08/1937</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[high] Ava Clarke</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[high] Hospital Number: 9999006</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[high] NHS Number: 9998009006</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[high] Female</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[high] Relevant history includes history of breast cancer (treated).</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[high] history of breast cancer</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[high] Diagnosis: Villous adenoma with focal invasion</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[high] MRI pelvis on 31/10/2024</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[high] T1 sm2/3</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[high] N0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[high] EMVI negative</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[high] CRM clear</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 14/11/2024(i)</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>[high] Refer for colorectal surgical review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[high] DOB: 27/12/1947</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[high] Mason Barker</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[high] Hospital Number: 9999007</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[high] NHS Number: 9998009007</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[high] Male</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[high] Relevant history includes ischaemic heart disease.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>[high] Diagnosis: Tubular adenoma with HGD</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>[high] CT TAP on 14/06/2024</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>[high] multiple enlarged mesenteric nodes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[high] no distant metastases.</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>[high] upper rectum thickening with multiple enlarged mesenteric nodes; no distant metastases.</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>[high] Colorectal Multidisciplinary Meeting — 21/06/2024(i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>[high] DOB: 08/08/1951</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[high] Freida Smale</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[high] Hospital Number: 9999008</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[high] NHS Number: 9998009008</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[high] Female</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[high] Diagnosis: Right‑sided colonic tumour</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>[high] MRI pelvis on 30/07/2024</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>[high] T3a</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[high] N1c</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>[high] EMVI positive.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[high] CRM clear,</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>[high] Colorectal Multidisciplinary Meeting 20/08/2024(i)</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>[high] Plan neoadjuvant CRT</t>
+          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted.</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
         </is>
       </c>
     </row>

--- a/output/generated-database-cloud9.xlsx
+++ b/output/generated-database-cloud9.xlsx
@@ -453,28 +453,28 @@
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"30/03/1944 Age"</t>
+"DOB: 27/12/1947"</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"ZIAD AL-FARSI(b)"</t>
+"Mason Barker"</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Hospital Number: 9990002"</t>
+"Hospital Number: 9999007"</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"NHS Number: 9990000002"</t>
+"NHS Number: 9998009007"</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
@@ -484,172 +484,810 @@
 "Male"</t>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"lymphoma"</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"lymphoma"</t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
-"Diagnosis: ADENOCARCINOMA, NOT OTHERWISE SPECIFIED"</t>
+"Diagnosis: Tubular adenoma with HGD"</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25"</t>
-      </text>
-    </comment>
-    <comment ref="O2" authorId="0" shapeId="0">
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"Diagnosis: Tubular adenoma with HGD"</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CT TAP on 14/06/2024"</t>
+      </text>
+    </comment>
+    <comment ref="V2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"multiple enlarged mesenteric nodes"</t>
+      </text>
+    </comment>
+    <comment ref="X2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"CT TAP on 14/06/2024: upper rectum thickening with multiple enlarged mesenteric nodes; no distant metastases."</t>
+      </text>
+    </comment>
+    <comment ref="AA2" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"21/06/2024"</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 08/08/1951"</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Freida Smale"</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999008"</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009008"</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Female"</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Right‑sided colonic tumour"</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI pelvis on 30/07/2024"</t>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"T3a"</t>
+      </text>
+    </comment>
+    <comment ref="P3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"N1c"</t>
+      </text>
+    </comment>
+    <comment ref="Q3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"EMVI positive"</t>
+      </text>
+    </comment>
+    <comment ref="R3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CRM clear"</t>
+      </text>
+    </comment>
+    <comment ref="AA3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"20/08/2024"</t>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"neoadjuvant CRT"</t>
+      </text>
+    </comment>
+    <comment ref="AM3" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Plan neoadjuvant CRT"</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 18/03/1964"</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009009
+Oliver Turner
+Male"</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999009"</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009009"</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Male"</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Right‑sided colonic tumour
+Differentiation: Poorly differentiated"</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"13/03/2024"</t>
+      </text>
+    </comment>
+    <comment ref="X4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"no distant uptake"</t>
+      </text>
+    </comment>
+    <comment ref="Y4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"PET‑CT performed for ? Vasculitis"</t>
+      </text>
+    </comment>
+    <comment ref="Z4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"? Vasculitis"</t>
+      </text>
+    </comment>
+    <comment ref="AA4" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"10/04/2024"</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 20/06/1941"</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Freya Hall"</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999010"</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009010"</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Female"</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Sigmoid adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI pelvis on 14/08/2024"</t>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"T3b"</t>
+      </text>
+    </comment>
+    <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"N1"</t>
+      </text>
+    </comment>
+    <comment ref="Q5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"EMVI negative"</t>
+      </text>
+    </comment>
+    <comment ref="R5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CRM clear"</t>
+      </text>
+    </comment>
+    <comment ref="AA5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"18/09/2024"</t>
+      </text>
+    </comment>
+    <comment ref="AB5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"neoadjuvant CRT"</t>
+      </text>
+    </comment>
+    <comment ref="AM5" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Plan neoadjuvant CRT"</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 24/03/1957"</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Erin Hall"</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999011"</t>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009011"</t>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Female"</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Serrated adenoma with dysplasia"</t>
+      </text>
+    </comment>
+    <comment ref="T6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CT on 12/02/2025"</t>
+      </text>
+    </comment>
+    <comment ref="X6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"CT on 12/02/2025:  lesion in the low rectum, no metastases"</t>
+      </text>
+    </comment>
+    <comment ref="AA6" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"19/02/2025"</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 22/10/1958"</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009012 
+Emmile Franklin
+Male"</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999012"</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009012"</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Male"</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Sigmoid adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI pelvis on 11/05/2024"</t>
+      </text>
+    </comment>
+    <comment ref="O7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"T2"</t>
+      </text>
+    </comment>
+    <comment ref="P7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"N0"</t>
+      </text>
+    </comment>
+    <comment ref="Q7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"EMVI negative"</t>
+      </text>
+    </comment>
+    <comment ref="R7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CRM/ISP threatened"</t>
+      </text>
+    </comment>
+    <comment ref="AA7" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"18/05/2024"</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 28/04/1952"</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Leah Morris"</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999013"</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009013"</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Female"</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"breast cancer"</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"breast cancer"</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colpnoscopy, biopsy, MRI"</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colpnoscopy, biopsy, MRI"</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: MMR‑deficient rectal adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Colpnoscopy, biopsy, MRI"</t>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MMR‑deficient rectal adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="X8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"Known breast cancer, had PET-CT which also showed (29/12/2024): FDG‑avid lesion in the rectum, avid breast lesion. 
+Breast cancer being treated with curative intent"</t>
+      </text>
+    </comment>
+    <comment ref="Y8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"avid breast lesion"</t>
+      </text>
+    </comment>
+    <comment ref="Z8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"avid breast lesion"</t>
+      </text>
+    </comment>
+    <comment ref="AA8" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"12/01/2025"</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 20/06/1964"</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hannah Higgins"</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999014"</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009014"</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Female"</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Flexi sig lesion in the upper rectum, unable to reach TI"</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Flexi sig lesion in the upper rectum, unable to reach TI"</t>
+      </text>
+    </comment>
+    <comment ref="J9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"lesion in the upper rectum, unable to reach TI"</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: MMR‑deficient rectal adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: MMR‑deficient rectal adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MMR‑deficient rectal adenocarcinoma"</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI 22/2/24"</t>
+      </text>
+    </comment>
+    <comment ref="O9" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
 "T3c"</t>
       </text>
     </comment>
-    <comment ref="P2" authorId="0" shapeId="0">
+    <comment ref="P9" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
 "N1c"</t>
       </text>
     </comment>
-    <comment ref="Q2" authorId="0" shapeId="0">
+    <comment ref="Q9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"EMVI negative"</t>
+      </text>
+    </comment>
+    <comment ref="R9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CRM clear"</t>
+      </text>
+    </comment>
+    <comment ref="T9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CT 23/2/24"</t>
+      </text>
+    </comment>
+    <comment ref="X9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: MEDIUM]
+Source evidence:
+"CT 23/2/24 - suspicious liver lesion"</t>
+      </text>
+    </comment>
+    <comment ref="Y9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CT 23/2/24 - suspicious liver lesion"</t>
+      </text>
+    </comment>
+    <comment ref="Z9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CT 23/2/24 - suspicious liver lesion"</t>
+      </text>
+    </comment>
+    <comment ref="AA9" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"27/02/2024"</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"DOB: 27/03/1972"</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009015
+Ollie Armstrong
+Male"</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Hospital Number: 9999015"</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"NHS Number: 9998009015"</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Male"</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"Diagnosis: Right‑sided colonic tumour"</t>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"MRI pelvis on 01/12/2024"</t>
+      </text>
+    </comment>
+    <comment ref="O10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"T1"</t>
+      </text>
+    </comment>
+    <comment ref="Q10" authorId="0" shapeId="0">
       <text>
         <t>[Confidence: HIGH]
 Source evidence:
 "EMVI positive"</t>
       </text>
     </comment>
-    <comment ref="R2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CRM/ISP unsafe"</t>
-      </text>
-    </comment>
-    <comment ref="S2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"PSW clear"</t>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT 22/2/2025"</t>
-      </text>
-    </comment>
-    <comment ref="V2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT 22/2/2025: no lymphadenopathy."</t>
-      </text>
-    </comment>
-    <comment ref="X2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"CT 22/2/2025: no lymphadenopathy."</t>
-      </text>
-    </comment>
-    <comment ref="AA2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"07/03/2025"</t>
-      </text>
-    </comment>
-    <comment ref="AB2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated."</t>
-      </text>
-    </comment>
-    <comment ref="AU2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted."</t>
-      </text>
-    </comment>
-    <comment ref="AW2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
-      </text>
-    </comment>
-    <comment ref="AX2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
-      </text>
-    </comment>
-    <comment ref="AY2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
-      </text>
-    </comment>
-    <comment ref="AZ2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
-      </text>
-    </comment>
-    <comment ref="BA2" authorId="0" shapeId="0">
-      <text>
-        <t>[Confidence: HIGH]
-Source evidence:
-"MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus."</t>
+    <comment ref="R10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"CRM involved"</t>
+      </text>
+    </comment>
+    <comment ref="AA10" authorId="0" shapeId="0">
+      <text>
+        <t>[Confidence: HIGH]
+Source evidence:
+"05/01/2025"</t>
       </text>
     </comment>
   </commentList>
@@ -977,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS2"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.28515625" customWidth="1" min="1" max="1"/>
@@ -1470,143 +2108,58 @@
     </row>
     <row r="2" ht="75" customFormat="1" customHeight="1" s="28">
       <c r="A2" s="29" t="n">
-        <v>16161</v>
+        <v>17528</v>
       </c>
       <c r="B2" s="28" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="C2" s="28" t="n">
-        <v>9990002</v>
+        <v>9999007</v>
       </c>
       <c r="D2" s="28" t="n">
-        <v>9990000002</v>
+        <v>9998009007</v>
       </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" s="28" t="inlineStr">
-        <is>
-          <t>lymphoma</t>
-        </is>
-      </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="F2" s="28" t="n"/>
+      <c r="G2" s="28" t="n"/>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="28" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Tubular adenoma with HGD</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="I2" s="28" t="inlineStr">
-        <is>
-          <t>Colonoscopy complete</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>ADENOCARCINOMA, NOT OTHERWISE SPECIFIED</t>
-        </is>
-      </c>
-      <c r="L2" s="28" t="inlineStr">
-        <is>
-          <t>07/03/2025</t>
-        </is>
-      </c>
       <c r="M2" s="28" t="n"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>04/03/2025</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>3c</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1c</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>threatened</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>22/02/2025</t>
+          <t>14/06/2024</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>straight to surgery</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>4/3/25</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3c</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1c</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>threatened</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>clear</t>
+          <t>21/06/2024</t>
         </is>
       </c>
       <c r="BV2" s="1" t="n"/>
@@ -1625,6 +2178,683 @@
       <c r="CI2" s="1" t="n"/>
       <c r="CJ2" s="1" t="n"/>
     </row>
+    <row r="3" ht="75" customHeight="1">
+      <c r="A3" s="29" t="n">
+        <v>18848</v>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="n">
+        <v>9999008</v>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>9998009008</v>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="28" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Right-sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="28" t="n"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30/07/2024</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>20/08/2024</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>downstaging nCRT</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BV3" s="1" t="n"/>
+      <c r="BW3" s="1" t="n"/>
+      <c r="BX3" s="1" t="n"/>
+      <c r="BY3" s="1" t="n"/>
+      <c r="BZ3" s="1" t="n"/>
+      <c r="CA3" s="1" t="n"/>
+      <c r="CB3" s="1" t="n"/>
+      <c r="CC3" s="1" t="n"/>
+      <c r="CD3" s="1" t="n"/>
+      <c r="CE3" s="1" t="n"/>
+      <c r="CF3" s="1" t="n"/>
+      <c r="CG3" s="1" t="n"/>
+      <c r="CH3" s="1" t="n"/>
+      <c r="CI3" s="1" t="n"/>
+      <c r="CJ3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="75" customHeight="1">
+      <c r="A4" s="29" t="n">
+        <v>23454</v>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n">
+        <v>9999009</v>
+      </c>
+      <c r="D4" s="28" t="n">
+        <v>9998009009</v>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="1" t="n"/>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Poorly differentiated right-sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="28" t="n"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13/03/2024</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Vasculitis</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>10/04/2024</t>
+        </is>
+      </c>
+      <c r="BV4" s="1" t="n"/>
+      <c r="BW4" s="1" t="n"/>
+      <c r="BX4" s="1" t="n"/>
+      <c r="BY4" s="1" t="n"/>
+      <c r="BZ4" s="1" t="n"/>
+      <c r="CA4" s="1" t="n"/>
+      <c r="CB4" s="1" t="n"/>
+      <c r="CC4" s="1" t="n"/>
+      <c r="CD4" s="1" t="n"/>
+      <c r="CE4" s="1" t="n"/>
+      <c r="CF4" s="1" t="n"/>
+      <c r="CG4" s="1" t="n"/>
+      <c r="CH4" s="1" t="n"/>
+      <c r="CI4" s="1" t="n"/>
+      <c r="CJ4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="75" customHeight="1">
+      <c r="A5" s="29" t="n">
+        <v>15147</v>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>9999010</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>9998009010</v>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="1" t="n"/>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>Sigmoid adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>14/08/2024</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>18/09/2024</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>downstaging nCRT</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BV5" s="1" t="n"/>
+      <c r="BW5" s="1" t="n"/>
+      <c r="BX5" s="1" t="n"/>
+      <c r="BY5" s="1" t="n"/>
+      <c r="BZ5" s="1" t="n"/>
+      <c r="CA5" s="1" t="n"/>
+      <c r="CB5" s="1" t="n"/>
+      <c r="CC5" s="1" t="n"/>
+      <c r="CD5" s="1" t="n"/>
+      <c r="CE5" s="1" t="n"/>
+      <c r="CF5" s="1" t="n"/>
+      <c r="CG5" s="1" t="n"/>
+      <c r="CH5" s="1" t="n"/>
+      <c r="CI5" s="1" t="n"/>
+      <c r="CJ5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="75" customHeight="1">
+      <c r="A6" s="29" t="n">
+        <v>20903</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>9999011</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>9998009011</v>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Serrated adenoma with dysplasia</t>
+        </is>
+      </c>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12/02/2025</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>19/02/2025</t>
+        </is>
+      </c>
+      <c r="BV6" s="1" t="n"/>
+      <c r="BW6" s="1" t="n"/>
+      <c r="BX6" s="1" t="n"/>
+      <c r="BY6" s="1" t="n"/>
+      <c r="BZ6" s="1" t="n"/>
+      <c r="CA6" s="1" t="n"/>
+      <c r="CB6" s="1" t="n"/>
+      <c r="CC6" s="1" t="n"/>
+      <c r="CD6" s="1" t="n"/>
+      <c r="CE6" s="1" t="n"/>
+      <c r="CF6" s="1" t="n"/>
+      <c r="CG6" s="1" t="n"/>
+      <c r="CH6" s="1" t="n"/>
+      <c r="CI6" s="1" t="n"/>
+      <c r="CJ6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="75" customHeight="1">
+      <c r="A7" s="29" t="n">
+        <v>21480</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>9999012</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>9998009012</v>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="1" t="n"/>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>Sigmoid adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>11/05/2024</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>threatened</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>18/05/2024</t>
+        </is>
+      </c>
+      <c r="BV7" s="1" t="n"/>
+      <c r="BW7" s="1" t="n"/>
+      <c r="BX7" s="1" t="n"/>
+      <c r="BY7" s="1" t="n"/>
+      <c r="BZ7" s="1" t="n"/>
+      <c r="CA7" s="1" t="n"/>
+      <c r="CB7" s="1" t="n"/>
+      <c r="CC7" s="1" t="n"/>
+      <c r="CD7" s="1" t="n"/>
+      <c r="CE7" s="1" t="n"/>
+      <c r="CF7" s="1" t="n"/>
+      <c r="CG7" s="1" t="n"/>
+      <c r="CH7" s="1" t="n"/>
+      <c r="CI7" s="1" t="n"/>
+      <c r="CJ7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="75" customHeight="1">
+      <c r="A8" s="29" t="n">
+        <v>19112</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>9999013</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>9998009013</v>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>breast</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Colonoscopy</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n"/>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="M8" s="28" t="inlineStr">
+        <is>
+          <t>Deficient</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>avid breast lesion</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="BV8" s="1" t="n"/>
+      <c r="BW8" s="1" t="n"/>
+      <c r="BX8" s="1" t="n"/>
+      <c r="BY8" s="1" t="n"/>
+      <c r="BZ8" s="1" t="n"/>
+      <c r="CA8" s="1" t="n"/>
+      <c r="CB8" s="1" t="n"/>
+      <c r="CC8" s="1" t="n"/>
+      <c r="CD8" s="1" t="n"/>
+      <c r="CE8" s="1" t="n"/>
+      <c r="CF8" s="1" t="n"/>
+      <c r="CG8" s="1" t="n"/>
+      <c r="CH8" s="1" t="n"/>
+      <c r="CI8" s="1" t="n"/>
+      <c r="CJ8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" s="29" t="n">
+        <v>23548</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>HH</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>9999014</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>9998009014</v>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>flexi sig</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>lesion in the upper rectum, unable to reach TI</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="M9" s="28" t="inlineStr">
+        <is>
+          <t>Deficient</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>22/02/2024</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3c</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23/02/2024</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>suspicious liver lesion</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>27/02/2024</t>
+        </is>
+      </c>
+      <c r="BV9" s="1" t="n"/>
+      <c r="BW9" s="1" t="n"/>
+      <c r="BX9" s="1" t="n"/>
+      <c r="BY9" s="1" t="n"/>
+      <c r="BZ9" s="1" t="n"/>
+      <c r="CA9" s="1" t="n"/>
+      <c r="CB9" s="1" t="n"/>
+      <c r="CC9" s="1" t="n"/>
+      <c r="CD9" s="1" t="n"/>
+      <c r="CE9" s="1" t="n"/>
+      <c r="CF9" s="1" t="n"/>
+      <c r="CG9" s="1" t="n"/>
+      <c r="CH9" s="1" t="n"/>
+      <c r="CI9" s="1" t="n"/>
+      <c r="CJ9" s="1" t="n"/>
+    </row>
+    <row r="10" ht="75" customHeight="1">
+      <c r="A10" s="29" t="n">
+        <v>26385</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>9999015</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>9998009015</v>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="1" t="n"/>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Right‑sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="L10" s="28" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>01/12/2024</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>involved</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>05/01/2025</t>
+        </is>
+      </c>
+      <c r="BV10" s="1" t="n"/>
+      <c r="BW10" s="1" t="n"/>
+      <c r="BX10" s="1" t="n"/>
+      <c r="BY10" s="1" t="n"/>
+      <c r="BZ10" s="1" t="n"/>
+      <c r="CA10" s="1" t="n"/>
+      <c r="CB10" s="1" t="n"/>
+      <c r="CC10" s="1" t="n"/>
+      <c r="CD10" s="1" t="n"/>
+      <c r="CE10" s="1" t="n"/>
+      <c r="CF10" s="1" t="n"/>
+      <c r="CG10" s="1" t="n"/>
+      <c r="CH10" s="1" t="n"/>
+      <c r="CI10" s="1" t="n"/>
+      <c r="CJ10" s="1" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1637,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,22 +3327,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[high] 30/03/1944 Age</t>
+          <t>[high] DOB: 27/12/1947</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[high] ZIAD AL-FARSI(b)</t>
+          <t>[high] Mason Barker</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[high] Hospital Number: 9990002</t>
+          <t>[high] Hospital Number: 9999007</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[high] NHS Number: 9990000002</t>
+          <t>[high] NHS Number: 9998009007</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2120,124 +3350,598 @@
           <t>[high] Male</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[high] lymphoma</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[high] lymphoma</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[high] Diagnosis: ADENOCARCINOMA, NOT OTHERWISE SPECIFIED</t>
+          <t>[high] Diagnosis: Tubular adenoma with HGD</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+          <t>[medium] Diagnosis: Tubular adenoma with HGD</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>[high] CT TAP on 14/06/2024</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>[medium] multiple enlarged mesenteric nodes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[medium] CT TAP on 14/06/2024: upper rectum thickening with multiple enlarged mesenteric nodes; no distant metastases.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[high] 21/06/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[high] DOB: 08/08/1951</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[high] Freida Smale</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999008</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009008</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[high] Female</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: Right‑sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[high] MRI pelvis on 30/07/2024</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>[high] T3a</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[high] N1c</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[high] EMVI positive</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[high] CRM clear</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[high] 20/08/2024</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[high] neoadjuvant CRT</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>[high] Plan neoadjuvant CRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>[high] DOB: 18/03/1964</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009009
+Oliver Turner
+Male</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999009</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009009</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[high] Male</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: Right‑sided colonic tumour
+Differentiation: Poorly differentiated</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>[high] 13/03/2024</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[medium] no distant uptake</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[high] PET‑CT performed for ? Vasculitis</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[high] ? Vasculitis</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[high] 10/04/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[high] DOB: 20/06/1941</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[high] Freya Hall</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999010</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009010</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[high] Female</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: Sigmoid adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[high] MRI pelvis on 14/08/2024</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>[high] T3b</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[high] N1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>[high] EMVI negative</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>[high] CRM clear</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[high] 18/09/2024</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>[high] neoadjuvant CRT</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>[high] Plan neoadjuvant CRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[high] DOB: 24/03/1957</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[high] Erin Hall</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999011</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009011</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[high] Female</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: Serrated adenoma with dysplasia</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>[high] CT on 12/02/2025</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[medium] CT on 12/02/2025:  lesion in the low rectum, no metastases</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>[high] 19/02/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[high] DOB: 22/10/1958</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009012 
+Emmile Franklin
+Male</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999012</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009012</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[high] Male</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: Sigmoid adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[high] MRI pelvis on 11/05/2024</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>[high] T2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>[high] N0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>[high] EMVI negative</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>[high] CRM/ISP threatened</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>[high] 18/05/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[high] DOB: 28/04/1952</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[high] Leah Morris</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999013</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009013</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[high] Female</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[high] breast cancer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[high] breast cancer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[high] Colpnoscopy, biopsy, MRI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[high] Colpnoscopy, biopsy, MRI</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>[high] Colpnoscopy, biopsy, MRI</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>[high] MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[medium] Known breast cancer, had PET-CT which also showed (29/12/2024): FDG‑avid lesion in the rectum, avid breast lesion. 
+Breast cancer being treated with curative intent</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>[high] avid breast lesion</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>[high] avid breast lesion</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>[high] 12/01/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[high] DOB: 20/06/1964</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[high] Hannah Higgins</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999014</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009014</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[high] Female</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[high] Flexi sig lesion in the upper rectum, unable to reach TI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[high] Flexi sig lesion in the upper rectum, unable to reach TI</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[high] lesion in the upper rectum, unable to reach TI</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[high] MMR‑deficient rectal adenocarcinoma</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[high] MRI 22/2/24</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>[high] T3c</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>[high] N1c</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>[high] EMVI negative</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>[high] CRM clear</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>[high] CT 23/2/24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[medium] CT 23/2/24 - suspicious liver lesion</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>[high] CT 23/2/24 - suspicious liver lesion</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>[high] CT 23/2/24 - suspicious liver lesion</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>[high] 27/02/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>[high] DOB: 27/03/1972</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009015
+Ollie Armstrong
+Male</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[high] Hospital Number: 9999015</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[high] NHS Number: 9998009015</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[high] Male</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[high] Diagnosis: Right‑sided colonic tumour</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[high] MRI pelvis on 01/12/2024</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[high] T1</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>[high] EMVI positive</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[high] CRM/ISP unsafe</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>[high] PSW clear</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>[high] CT 22/2/2025</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>[high] CT 22/2/2025: no lymphadenopathy.</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[high] CT 22/2/2025: no lymphadenopathy.</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>[high] 07/03/2025</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>[high] Colonoscopy: polypoidal lesion in the low rectum, biopsy adenocarcinoma, poorly differentiated.</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted.</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>[high] MRI 4/3/25 – low rectal lesion with a low signal stalk, area of ulceration noted. Some high signal change consistent with mucus.</t>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[high] CRM involved</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>[high] 05/01/2025</t>
         </is>
       </c>
     </row>
